--- a/products/freelance-invoice-income-tracker.xlsx
+++ b/products/freelance-invoice-income-tracker.xlsx
@@ -15,7 +15,11 @@
     <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$M$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Income Log'!$A$1:$G$40</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Invoice!$A$1:$D$35</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Settings!$A$1:$D$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$26</definedName>
     <definedName function="false" hidden="false" name="ClientList" vbProcedure="false">Settings!$A$18:$A$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="110">
   <si>
     <t xml:space="preserve">Freelance Invoice + Income Tracker</t>
   </si>
@@ -276,6 +280,18 @@
     <t xml:space="preserve">INVOICES SENT</t>
   </si>
   <si>
+    <t xml:space="preserve">AVG DAYS TO PAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLLECTION RATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVG INVOICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVERDUE AMOUNT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Invoiced by month</t>
   </si>
   <si>
@@ -325,20 +341,42 @@
   </si>
   <si>
     <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarter by quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
     <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -660,7 +698,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -833,6 +871,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -841,7 +891,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -849,7 +899,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,7 +1072,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!C11</c:f>
+              <c:f>Dashboard!C14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1067,7 +1117,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$B$12:$B$23</c:f>
+              <c:f>Dashboard!$B$15:$B$26</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1111,7 +1161,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$C$12:$C$23</c:f>
+              <c:f>Dashboard!$C$15:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1157,11 +1207,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25708349"/>
-        <c:axId val="34290226"/>
+        <c:axId val="94434206"/>
+        <c:axId val="95124837"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25708349"/>
+        <c:axId val="94434206"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1193,7 +1243,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34290226"/>
+        <c:crossAx val="95124837"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1201,7 +1251,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34290226"/>
+        <c:axId val="95124837"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1243,7 +1293,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25708349"/>
+        <c:crossAx val="94434206"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1275,15 +1325,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>65520</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1132560</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -1292,7 +1342,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3378240" y="5133960"/>
+        <a:off x="355680" y="7153200"/>
         <a:ext cx="5399640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1485,7 +1535,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF2E9E8F"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1642,8 +1692,8 @@
     <mergeCell ref="C18:H18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1655,7 +1705,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1909,8 +1959,8 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2221,7 +2271,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3255,8 +3305,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3268,9 +3318,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF2E9E8F"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -3364,353 +3414,465 @@
       </c>
       <c r="L7" s="42"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+    <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="C9" s="38"/>
+      <c r="E9" s="38" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="F9" s="38"/>
+      <c r="H9" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="I9" s="38"/>
+      <c r="K9" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="L9" s="38"/>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="43" t="n">
+        <f aca="false">IFERROR(ROUND(SUMPRODUCT(('Income Log'!$G$6:$G$105-'Income Log'!$A$6:$A$105)*('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4))/SUMPRODUCT(('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4)*1),1),"—")</f>
+        <v>10</v>
+      </c>
+      <c r="C10" s="43"/>
+      <c r="E10" s="44" t="n">
+        <f aca="false">IF(B7=0,"",E7/B7)</f>
+        <v>0.797979797979798</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="H10" s="45" t="n">
+        <f aca="false">IF(K7=0,"",B7/K7)</f>
+        <v>990</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="K10" s="41" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Overdue",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="41"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H13" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="n">
+      <c r="I14" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A12,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A12+1,1))</f>
+      <c r="B15" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A15,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
         <v>1520</v>
       </c>
-      <c r="H12" s="44" t="str">
+      <c r="H15" s="47" t="str">
         <f aca="false">IF(Settings!A18="","",Settings!A18)</f>
         <v>Acme Studios</v>
       </c>
-      <c r="I12" s="45" t="n">
-        <f aca="false">IF($H12="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H12,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="I15" s="48" t="n">
+        <f aca="false">IF($H15="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H15,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>2120</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A13,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A13+1,1))</f>
+      <c r="B16" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A16,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
         <v>850</v>
       </c>
-      <c r="H13" s="44" t="str">
+      <c r="H16" s="47" t="str">
         <f aca="false">IF(Settings!A19="","",Settings!A19)</f>
         <v>Beacon Coffee Co.</v>
       </c>
-      <c r="I13" s="45" t="n">
-        <f aca="false">IF($H13="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H13,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="I16" s="48" t="n">
+        <f aca="false">IF($H16="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H16,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>850</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A14,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A14+1,1))</f>
+      <c r="B17" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A17,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
         <v>600</v>
       </c>
-      <c r="H14" s="44" t="str">
+      <c r="H17" s="47" t="str">
         <f aca="false">IF(Settings!A20="","",Settings!A20)</f>
         <v/>
       </c>
-      <c r="I14" s="45" t="str">
-        <f aca="false">IF($H14="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H14,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="n">
+      <c r="I17" s="48" t="str">
+        <f aca="false">IF($H17="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H17,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A15,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="44" t="str">
-        <f aca="false">IF(Settings!A21="","",Settings!A21)</f>
-        <v/>
-      </c>
-      <c r="I15" s="45" t="str">
-        <f aca="false">IF($H15="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H15,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A16,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="44" t="str">
-        <f aca="false">IF(Settings!A22="","",Settings!A22)</f>
-        <v/>
-      </c>
-      <c r="I16" s="45" t="str">
-        <f aca="false">IF($H16="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H16,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="45" t="n">
-        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A17,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="44" t="str">
-        <f aca="false">IF(Settings!A23="","",Settings!A23)</f>
-        <v/>
-      </c>
-      <c r="I17" s="45" t="str">
-        <f aca="false">IF($H17="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H17,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="45" t="n">
+      <c r="B18" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A18,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="44" t="str">
-        <f aca="false">IF(Settings!A24="","",Settings!A24)</f>
-        <v/>
-      </c>
-      <c r="I18" s="45" t="str">
+      <c r="H18" s="47" t="str">
+        <f aca="false">IF(Settings!A21="","",Settings!A21)</f>
+        <v/>
+      </c>
+      <c r="I18" s="48" t="str">
         <f aca="false">IF($H18="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H18,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="45" t="n">
+      <c r="A19" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A19,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="44" t="str">
-        <f aca="false">IF(Settings!A25="","",Settings!A25)</f>
-        <v/>
-      </c>
-      <c r="I19" s="45" t="str">
+      <c r="H19" s="47" t="str">
+        <f aca="false">IF(Settings!A22="","",Settings!A22)</f>
+        <v/>
+      </c>
+      <c r="I19" s="48" t="str">
         <f aca="false">IF($H19="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H19,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="45" t="n">
+      <c r="A20" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A20,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="44" t="str">
-        <f aca="false">IF(Settings!A26="","",Settings!A26)</f>
-        <v/>
-      </c>
-      <c r="I20" s="45" t="str">
+      <c r="H20" s="47" t="str">
+        <f aca="false">IF(Settings!A23="","",Settings!A23)</f>
+        <v/>
+      </c>
+      <c r="I20" s="48" t="str">
         <f aca="false">IF($H20="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H20,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="45" t="n">
+      <c r="A21" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A21,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="44" t="str">
-        <f aca="false">IF(Settings!A27="","",Settings!A27)</f>
-        <v/>
-      </c>
-      <c r="I21" s="45" t="str">
+      <c r="H21" s="47" t="str">
+        <f aca="false">IF(Settings!A24="","",Settings!A24)</f>
+        <v/>
+      </c>
+      <c r="I21" s="48" t="str">
         <f aca="false">IF($H21="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H21,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="45" t="n">
+      <c r="A22" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A22,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="46" t="str">
-        <f aca="false">IF(Settings!A28="","",Settings!A28)</f>
-        <v/>
-      </c>
-      <c r="I22" s="47" t="str">
+      <c r="H22" s="47" t="str">
+        <f aca="false">IF(Settings!A25="","",Settings!A25)</f>
+        <v/>
+      </c>
+      <c r="I22" s="48" t="str">
         <f aca="false">IF($H22="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H22,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="n">
-        <v>12</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="45" t="n">
+      <c r="A23" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A23,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="46" t="str">
+      <c r="H23" s="47" t="str">
+        <f aca="false">IF(Settings!A26="","",Settings!A26)</f>
+        <v/>
+      </c>
+      <c r="I23" s="48" t="str">
+        <f aca="false">IF($H23="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H23,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A24,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A24+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="47" t="str">
+        <f aca="false">IF(Settings!A27="","",Settings!A27)</f>
+        <v/>
+      </c>
+      <c r="I24" s="48" t="str">
+        <f aca="false">IF($H24="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H24,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="46" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A25,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A25+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="49" t="str">
+        <f aca="false">IF(Settings!A28="","",Settings!A28)</f>
+        <v/>
+      </c>
+      <c r="I25" s="50" t="str">
+        <f aca="false">IF($H25="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H25,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A26,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A26+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="49" t="str">
         <f aca="false">IF(Settings!A29="","",Settings!A29)</f>
         <v/>
       </c>
-      <c r="I23" s="47" t="str">
-        <f aca="false">IF($H23="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H23,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H24" s="46" t="str">
+      <c r="I26" s="50" t="str">
+        <f aca="false">IF($H26="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H26,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="49" t="str">
         <f aca="false">IF(Settings!A30="","",Settings!A30)</f>
         <v/>
       </c>
-      <c r="I24" s="47" t="str">
-        <f aca="false">IF($H24="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H24,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="46" t="str">
+      <c r="I27" s="50" t="str">
+        <f aca="false">IF($H27="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H27,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="49" t="str">
         <f aca="false">IF(Settings!A31="","",Settings!A31)</f>
         <v/>
       </c>
-      <c r="I25" s="47" t="str">
-        <f aca="false">IF($H25="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H25,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="46" t="str">
+      <c r="I28" s="50" t="str">
+        <f aca="false">IF($H28="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H28,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="49" t="str">
         <f aca="false">IF(Settings!A32="","",Settings!A32)</f>
         <v/>
       </c>
-      <c r="I26" s="47" t="str">
-        <f aca="false">IF($H26="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H26,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="46" t="str">
+      <c r="I29" s="50" t="str">
+        <f aca="false">IF($H29="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H29,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
+        <v>2970</v>
+      </c>
+      <c r="D30" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
+        <v>2370</v>
+      </c>
+      <c r="H30" s="49" t="str">
         <f aca="false">IF(Settings!A33="","",Settings!A33)</f>
         <v/>
       </c>
-      <c r="I27" s="47" t="str">
-        <f aca="false">IF($H27="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H27,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="46" t="str">
+      <c r="I30" s="50" t="str">
+        <f aca="false">IF($H30="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H30,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="49" t="str">
         <f aca="false">IF(Settings!A34="","",Settings!A34)</f>
         <v/>
       </c>
-      <c r="I28" s="47" t="str">
-        <f aca="false">IF($H28="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H28,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H29" s="46" t="str">
+      <c r="I31" s="50" t="str">
+        <f aca="false">IF($H31="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H31,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="49" t="str">
         <f aca="false">IF(Settings!A35="","",Settings!A35)</f>
         <v/>
       </c>
-      <c r="I29" s="47" t="str">
-        <f aca="false">IF($H29="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H29,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H30" s="46" t="str">
+      <c r="I32" s="50" t="str">
+        <f aca="false">IF($H32="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H32,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="48" t="n">
+        <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="49" t="str">
         <f aca="false">IF(Settings!A36="","",Settings!A36)</f>
         <v/>
       </c>
-      <c r="I30" s="47" t="str">
-        <f aca="false">IF($H30="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H30,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="46" t="str">
+      <c r="I33" s="50" t="str">
+        <f aca="false">IF($H33="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H33,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="49" t="str">
         <f aca="false">IF(Settings!A37="","",Settings!A37)</f>
         <v/>
       </c>
-      <c r="I31" s="47" t="str">
-        <f aca="false">IF($H31="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H31,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="I34" s="50" t="str">
+        <f aca="false">IF($H34="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H34,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="18">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B6:C6"/>
@@ -3721,10 +3883,18 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/products/freelance-invoice-income-tracker.xlsx
+++ b/products/freelance-invoice-income-tracker.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Income Log'!$A$1:$G$40</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Invoice!$A$1:$D$35</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Settings!$A$1:$D$38</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$26</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$27</definedName>
     <definedName function="false" hidden="false" name="ClientList" vbProcedure="false">Settings!$A$18:$A$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="111">
   <si>
     <t xml:space="preserve">Freelance Invoice + Income Tracker</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t xml:space="preserve">Works in Microsoft Excel (2016 or newer) and Google Sheets (upload to Drive, then Open with Google Sheets).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulas are protected so you can't break anything by accident — every cell meant for typing is unlocked. To change anything else: Review → Unprotect Sheet (no password).</t>
   </si>
   <si>
     <t xml:space="preserve">Settings</t>
@@ -743,17 +746,17 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -775,13 +778,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -791,9 +794,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -827,29 +830,29 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
@@ -1207,11 +1210,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94434206"/>
-        <c:axId val="95124837"/>
+        <c:axId val="25787640"/>
+        <c:axId val="94753621"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94434206"/>
+        <c:axId val="25787640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1243,7 +1246,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95124837"/>
+        <c:crossAx val="94753621"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1251,7 +1254,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95124837"/>
+        <c:axId val="94753621"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1293,7 +1296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94434206"/>
+        <c:crossAx val="25787640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1534,10 +1537,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF2E9E8F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1681,7 +1683,13 @@
         <v>16</v>
       </c>
     </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -1704,7 +1712,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
@@ -1720,7 +1727,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1732,7 +1739,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1744,123 +1751,123 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>0.085</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1954,6 +1961,7 @@
       <c r="C37" s="11"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -1971,7 +1979,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D34"/>
@@ -2011,7 +2018,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2019,21 +2026,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="20" t="n">
         <v>46083</v>
@@ -2045,7 +2052,7 @@
         <v>billing@acmestudios.com</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="22" t="n">
         <f aca="false">IF($D$8="","",$D$8+Settings!$B$14)</f>
@@ -2060,21 +2067,21 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -2089,7 +2096,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>2</v>
@@ -2194,7 +2201,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D26" s="26" t="n">
         <f aca="false">SUM(D13:D24)</f>
@@ -2213,7 +2220,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="29" t="n">
         <f aca="false">D26+D27</f>
@@ -2222,7 +2229,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2236,13 +2243,14 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -2270,7 +2278,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H105"/>
@@ -2288,7 +2295,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2300,7 +2307,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2312,30 +2319,30 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2343,19 +2350,19 @@
         <v>46034</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>1520</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="32" t="n">
         <v>46042</v>
@@ -2366,19 +2373,19 @@
         <v>46056</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="37" t="n">
         <v>850</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="35" t="n">
         <v>46068</v>
@@ -2389,19 +2396,19 @@
         <v>46083</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>600</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="32"/>
     </row>
@@ -3279,6 +3286,7 @@
       <c r="G105" s="35"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -3317,7 +3325,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF2E9E8F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
@@ -3336,7 +3343,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3352,7 +3359,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3368,7 +3375,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>2026</v>
@@ -3376,19 +3383,19 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="38"/>
       <c r="E6" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="38"/>
       <c r="H6" s="38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I6" s="38"/>
       <c r="K6" s="38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L6" s="38"/>
     </row>
@@ -3417,19 +3424,19 @@
     <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="38"/>
       <c r="E9" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F9" s="38"/>
       <c r="H9" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" s="38"/>
       <c r="K9" s="38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L9" s="38"/>
     </row>
@@ -3457,27 +3464,27 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3485,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A15,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
@@ -3505,7 +3512,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A16,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
@@ -3525,7 +3532,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A17,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
@@ -3545,7 +3552,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A18,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
@@ -3565,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A19,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
@@ -3585,7 +3592,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A20,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
@@ -3605,7 +3612,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A21,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
@@ -3625,7 +3632,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A22,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
@@ -3645,7 +3652,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A23,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
@@ -3665,7 +3672,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C24" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A24,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A24+1,1))</f>
@@ -3685,7 +3692,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A25,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A25+1,1))</f>
@@ -3705,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A26,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A26+1,1))</f>
@@ -3732,7 +3739,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="49" t="str">
         <f aca="false">IF(Settings!A31="","",Settings!A31)</f>
@@ -3745,16 +3752,16 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H29" s="49" t="str">
         <f aca="false">IF(Settings!A32="","",Settings!A32)</f>
@@ -3770,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
@@ -3794,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C31" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
@@ -3818,7 +3825,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
@@ -3842,7 +3849,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" s="48" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
@@ -3872,6 +3879,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="18">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>

--- a/products/freelance-invoice-income-tracker.xlsx
+++ b/products/freelance-invoice-income-tracker.xlsx
@@ -408,14 +408,14 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFE5E7EB"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -423,14 +423,14 @@
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FF1F2937"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -438,14 +438,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -453,7 +453,7 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -461,7 +461,7 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -469,7 +469,7 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -477,7 +477,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -485,14 +485,14 @@
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF1F3A5F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -500,7 +500,7 @@
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FF2E9E8F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -508,7 +508,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -516,7 +516,7 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF1F3A5F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -524,7 +524,7 @@
       <b val="true"/>
       <sz val="14"/>
       <color rgb="FF2E9E8F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -532,7 +532,7 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF1F3A5F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -540,7 +540,7 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF2E9E8F"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -548,7 +548,7 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FFB3352C"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -556,14 +556,14 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF1F2937"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF6B7280"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -581,7 +581,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -596,6 +596,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF4F7FA"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF6DE"/>
         <bgColor rgb="FFFFF1D6"/>
       </patternFill>
@@ -603,13 +609,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFF9FAFC"/>
+        <bgColor rgb="FFF4F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9FAFC"/>
-        <bgColor rgb="FFF4F6FA"/>
+        <bgColor rgb="FFF4F7FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -701,7 +707,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -710,138 +716,142 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -854,55 +864,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -918,7 +940,7 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="Calibri"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
@@ -933,7 +955,7 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="Calibri"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
@@ -948,7 +970,7 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="Calibri"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
@@ -978,7 +1000,7 @@
       <rgbColor rgb="FF92600A"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1B7A46"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFE5E7EB"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -997,12 +1019,12 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF4F6FA"/>
+      <rgbColor rgb="FFF4F7FA"/>
       <rgbColor rgb="FFDCF3E4"/>
       <rgbColor rgb="FFFFF1D6"/>
-      <rgbColor rgb="FFE5E7EB"/>
+      <rgbColor rgb="FFE4E9E6"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFF9FAFC"/>
-      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFBE3E1"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1210,11 +1232,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25787640"/>
-        <c:axId val="94753621"/>
+        <c:axId val="46652681"/>
+        <c:axId val="12331454"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25787640"/>
+        <c:axId val="46652681"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1246,7 +1268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94753621"/>
+        <c:crossAx val="12331454"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1254,7 +1276,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94753621"/>
+        <c:axId val="12331454"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1264,7 +1286,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e4e9e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1296,7 +1318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25787640"/>
+        <c:crossAx val="46652681"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1315,10 +1337,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -1334,10 +1353,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1132560</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>747720</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1345,7 +1364,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="355680" y="7153200"/>
+        <a:off x="281880" y="7648560"/>
         <a:ext cx="5399640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1539,8 +1558,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
@@ -1558,135 +1577,510 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6"/>
-      <c r="C21" s="7" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8"/>
-      <c r="C22" s="7" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="9" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="10" t="s">
         <v>17</v>
       </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -1714,8 +2108,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -1738,227 +2132,478 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>28</v>
       </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>0.085</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="15" t="s">
         <v>39</v>
       </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -1982,7 +2627,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
@@ -1990,264 +2635,264 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="str">
+      <c r="A1" s="17" t="str">
         <f aca="false">IF(Settings!B5="","Your Business Name",Settings!B5)</f>
         <v>Alex Rivera Design</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="str">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="str">
         <f aca="false">IF(Settings!B6="","",Settings!B6&amp;"   ·   "&amp;Settings!B7)</f>
         <v>alex@riveradesign.com   ·   (555) 010-2266</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="str">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="str">
         <f aca="false">IF(Settings!B8="","",Settings!B8)</f>
         <v>410 Maple Ave, Portland, OR</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="22" t="n">
         <v>46083</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="str">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="str">
         <f aca="false">IFERROR(INDEX(Settings!$B$18:$B$37,MATCH($A$8,Settings!$A$18:$A$37,0)),"")</f>
         <v>billing@acmestudios.com</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">IF($D$8="","",$D$8+Settings!$B$14)</f>
         <v>46097</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="str">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="str">
         <f aca="false">IFERROR(INDEX(Settings!$C$18:$C$37,MATCH($A$8,Settings!$A$18:$A$37,0)),"")</f>
         <v>Acme Studios LLC</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="25" t="n">
         <v>600</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">IF(OR($B13="",$C13=""),"",ROUND($B13*$C13,2))</f>
         <v>600</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="26" t="n">
         <f aca="false">IF(OR($B14="",$C14=""),"",ROUND($B14*$C14,2))</f>
         <v>160</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24" t="str">
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26" t="str">
         <f aca="false">IF(OR($B15="",$C15=""),"",ROUND($B15*$C15,2))</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24" t="str">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26" t="str">
         <f aca="false">IF(OR($B16="",$C16=""),"",ROUND($B16*$C16,2))</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24" t="str">
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="26" t="str">
         <f aca="false">IF(OR($B17="",$C17=""),"",ROUND($B17*$C17,2))</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="24" t="str">
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="26" t="str">
         <f aca="false">IF(OR($B18="",$C18=""),"",ROUND($B18*$C18,2))</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24" t="str">
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="26" t="str">
         <f aca="false">IF(OR($B19="",$C19=""),"",ROUND($B19*$C19,2))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24" t="str">
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26" t="str">
         <f aca="false">IF(OR($B20="",$C20=""),"",ROUND($B20*$C20,2))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24" t="str">
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26" t="str">
         <f aca="false">IF(OR($B21="",$C21=""),"",ROUND($B21*$C21,2))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24" t="str">
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26" t="str">
         <f aca="false">IF(OR($B22="",$C22=""),"",ROUND($B22*$C22,2))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="24" t="str">
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26" t="str">
         <f aca="false">IF(OR($B23="",$C23=""),"",ROUND($B23*$C23,2))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24" t="str">
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26" t="str">
         <f aca="false">IF(OR($B24="",$C24=""),"",ROUND($B24*$C24,2))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="25" t="s">
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="28" t="n">
         <f aca="false">SUM(D13:D24)</f>
         <v>760</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="7" t="str">
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="29" t="str">
         <f aca="false">"Tax ("&amp;TEXT(Settings!$B$12,"0.0%")&amp;")"</f>
         <v>Tax (8.5%)</v>
       </c>
-      <c r="D27" s="27" t="n">
+      <c r="D27" s="30" t="n">
         <f aca="false">ROUND(D26*Settings!$B$12,2)</f>
         <v>64.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="32" t="n">
         <f aca="false">D26+D27</f>
         <v>824.6</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="str">
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="str">
         <f aca="false">IF(Settings!B9="","",Settings!B9)</f>
         <v>Pay by bank transfer to a/c 0000-1111 or PayPal alex@riveradesign.com</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="s">
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -2281,7 +2926,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
@@ -2306,984 +2951,984 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="35" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="n">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="36" t="n">
         <v>46034</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="38" t="n">
         <v>1520</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="36" t="n">
         <v>46042</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="n">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="n">
         <v>46056</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="41" t="n">
         <v>850</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="39" t="n">
         <v>46068</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="n">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36" t="n">
         <v>46083</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="38" t="n">
         <v>600</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="35"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="35"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="35"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="35"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="35"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="35"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="32"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="35"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="32"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="35"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="32"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="35"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="32"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="35"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="32"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="35"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="32"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="35"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="32"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="35"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="32"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="35"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="32"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="32"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="35"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="32"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="32"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="35"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="32"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="32"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="35"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="35"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="32"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="32"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="35"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="35"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="32"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="35"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="35"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="32"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="32"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="35"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="35"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="32"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="32"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="35"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="35"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="32"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="32"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="35"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="35"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="32"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="32"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="35"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="35"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="32"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="35"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="35"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="32"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="35"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="35"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="32"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="35"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="35"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="32"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="32"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="35"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="35"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="32"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="35"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="35"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="32"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="33"/>
-      <c r="G64" s="32"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="35"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="35"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="32"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="32"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="35"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="35"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="32"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="33"/>
-      <c r="G68" s="32"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="35"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="35"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="32"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="33"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="32"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="35"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="35"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="32"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="32"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="35"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="32"/>
-      <c r="B74" s="33"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="32"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="35"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="32"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="34"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="32"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="36"/>
-      <c r="G77" s="35"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="32"/>
-      <c r="B78" s="33"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="34"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="32"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="35"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="32"/>
-      <c r="B80" s="33"/>
-      <c r="C80" s="33"/>
-      <c r="D80" s="33"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="33"/>
-      <c r="G80" s="32"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="36"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="36"/>
-      <c r="G81" s="35"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="32"/>
-      <c r="B82" s="33"/>
-      <c r="C82" s="33"/>
-      <c r="D82" s="33"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="32"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="35"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="36"/>
-      <c r="D83" s="36"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="36"/>
-      <c r="G83" s="35"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="32"/>
-      <c r="B84" s="33"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="33"/>
-      <c r="E84" s="34"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="32"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="35"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="36"/>
-      <c r="G85" s="35"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="32"/>
-      <c r="B86" s="33"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="34"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="32"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="35"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="36"/>
-      <c r="D87" s="36"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="36"/>
-      <c r="G87" s="35"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="32"/>
-      <c r="B88" s="33"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="33"/>
-      <c r="E88" s="34"/>
-      <c r="F88" s="33"/>
-      <c r="G88" s="32"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="35"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="36"/>
-      <c r="G89" s="35"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="32"/>
-      <c r="B90" s="33"/>
-      <c r="C90" s="33"/>
-      <c r="D90" s="33"/>
-      <c r="E90" s="34"/>
-      <c r="F90" s="33"/>
-      <c r="G90" s="32"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="35"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="36"/>
-      <c r="D91" s="36"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="35"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="32"/>
-      <c r="B92" s="33"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="33"/>
-      <c r="E92" s="34"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="32"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="35"/>
-      <c r="B93" s="36"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="36"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="36"/>
-      <c r="G93" s="35"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="32"/>
-      <c r="B94" s="33"/>
-      <c r="C94" s="33"/>
-      <c r="D94" s="33"/>
-      <c r="E94" s="34"/>
-      <c r="F94" s="33"/>
-      <c r="G94" s="32"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="35"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="37"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="35"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="32"/>
-      <c r="B96" s="33"/>
-      <c r="C96" s="33"/>
-      <c r="D96" s="33"/>
-      <c r="E96" s="34"/>
-      <c r="F96" s="33"/>
-      <c r="G96" s="32"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="35"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="35"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="32"/>
-      <c r="B98" s="33"/>
-      <c r="C98" s="33"/>
-      <c r="D98" s="33"/>
-      <c r="E98" s="34"/>
-      <c r="F98" s="33"/>
-      <c r="G98" s="32"/>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="35"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="35"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="32"/>
-      <c r="B100" s="33"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="33"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="33"/>
-      <c r="G100" s="32"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="35"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="37"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="35"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="32"/>
-      <c r="B102" s="33"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="34"/>
-      <c r="F102" s="33"/>
-      <c r="G102" s="32"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="35"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="36"/>
-      <c r="D103" s="36"/>
-      <c r="E103" s="37"/>
-      <c r="F103" s="36"/>
-      <c r="G103" s="35"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="32"/>
-      <c r="B104" s="33"/>
-      <c r="C104" s="33"/>
-      <c r="D104" s="33"/>
-      <c r="E104" s="34"/>
-      <c r="F104" s="33"/>
-      <c r="G104" s="32"/>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="35"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="36"/>
-      <c r="D105" s="36"/>
-      <c r="E105" s="37"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="35"/>
+      <c r="G8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="39"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="36"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="36"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="39"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="39"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="39"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="36"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="39"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="36"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="36"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="39"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="36"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="36"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="39"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="36"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="39"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="36"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="36"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="39"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="36"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="39"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="36"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="39"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="36"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="36"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="39"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="39"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="36"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="39"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="36"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="39"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="36"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="39"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="39"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="36"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="36"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="39"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="36"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="36"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="39"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="39"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="36"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="39"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="39"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="36"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="36"/>
+    </row>
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="39"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="39"/>
+    </row>
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="36"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="36"/>
+    </row>
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="39"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="39"/>
+    </row>
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="36"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="36"/>
+    </row>
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="39"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="39"/>
+    </row>
+    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="36"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="36"/>
+    </row>
+    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="39"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="39"/>
+    </row>
+    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="36"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="36"/>
+    </row>
+    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="39"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="39"/>
+    </row>
+    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="36"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="36"/>
+    </row>
+    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="39"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="39"/>
+    </row>
+    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="36"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="36"/>
+    </row>
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="39"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="39"/>
+    </row>
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="36"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="36"/>
+    </row>
+    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="39"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="39"/>
+    </row>
+    <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="36"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="36"/>
+    </row>
+    <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="39"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="39"/>
+    </row>
+    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="36"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="36"/>
+    </row>
+    <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="39"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="39"/>
+    </row>
+    <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="36"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="36"/>
+    </row>
+    <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="39"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="39"/>
+    </row>
+    <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="36"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="36"/>
+    </row>
+    <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="39"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="39"/>
+    </row>
+    <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="36"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="36"/>
+    </row>
+    <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="39"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="39"/>
+    </row>
+    <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="36"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="36"/>
+    </row>
+    <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="39"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="39"/>
+    </row>
+    <row r="74" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="36"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="36"/>
+    </row>
+    <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="39"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="39"/>
+    </row>
+    <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="36"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="36"/>
+    </row>
+    <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="39"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="39"/>
+    </row>
+    <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="36"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="36"/>
+    </row>
+    <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="39"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="39"/>
+    </row>
+    <row r="80" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="36"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="36"/>
+    </row>
+    <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="39"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="39"/>
+    </row>
+    <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="36"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="36"/>
+    </row>
+    <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="39"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="39"/>
+    </row>
+    <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="36"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="36"/>
+    </row>
+    <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="39"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="39"/>
+    </row>
+    <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="36"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="36"/>
+    </row>
+    <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="39"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="39"/>
+    </row>
+    <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="36"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
+      <c r="D88" s="37"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="36"/>
+    </row>
+    <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="39"/>
+      <c r="B89" s="40"/>
+      <c r="C89" s="40"/>
+      <c r="D89" s="40"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="40"/>
+      <c r="G89" s="39"/>
+    </row>
+    <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="36"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="36"/>
+    </row>
+    <row r="91" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="39"/>
+      <c r="B91" s="40"/>
+      <c r="C91" s="40"/>
+      <c r="D91" s="40"/>
+      <c r="E91" s="41"/>
+      <c r="F91" s="40"/>
+      <c r="G91" s="39"/>
+    </row>
+    <row r="92" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="36"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="36"/>
+    </row>
+    <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="39"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="40"/>
+      <c r="E93" s="41"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="39"/>
+    </row>
+    <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="36"/>
+    </row>
+    <row r="95" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="39"/>
+      <c r="B95" s="40"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="40"/>
+      <c r="E95" s="41"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="39"/>
+    </row>
+    <row r="96" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="36"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="36"/>
+    </row>
+    <row r="97" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="39"/>
+      <c r="B97" s="40"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="40"/>
+      <c r="G97" s="39"/>
+    </row>
+    <row r="98" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="36"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="36"/>
+    </row>
+    <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="39"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="40"/>
+      <c r="D99" s="40"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="40"/>
+      <c r="G99" s="39"/>
+    </row>
+    <row r="100" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="36"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37"/>
+      <c r="D100" s="37"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="37"/>
+      <c r="G100" s="36"/>
+    </row>
+    <row r="101" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="39"/>
+      <c r="B101" s="40"/>
+      <c r="C101" s="40"/>
+      <c r="D101" s="40"/>
+      <c r="E101" s="41"/>
+      <c r="F101" s="40"/>
+      <c r="G101" s="39"/>
+    </row>
+    <row r="102" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="36"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="37"/>
+      <c r="D102" s="37"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="37"/>
+      <c r="G102" s="36"/>
+    </row>
+    <row r="103" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="39"/>
+      <c r="B103" s="40"/>
+      <c r="C103" s="40"/>
+      <c r="D103" s="40"/>
+      <c r="E103" s="41"/>
+      <c r="F103" s="40"/>
+      <c r="G103" s="39"/>
+    </row>
+    <row r="104" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="36"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="37"/>
+      <c r="E104" s="38"/>
+      <c r="F104" s="37"/>
+      <c r="G104" s="36"/>
+    </row>
+    <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="39"/>
+      <c r="B105" s="40"/>
+      <c r="C105" s="40"/>
+      <c r="D105" s="40"/>
+      <c r="E105" s="41"/>
+      <c r="F105" s="40"/>
+      <c r="G105" s="39"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
@@ -3327,8 +3972,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -3356,527 +4001,1131 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>2026</v>
       </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="38" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="H6" s="38" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="42"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="38"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="39" t="n">
+      <c r="A7" s="2"/>
+      <c r="B7" s="43" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>2970</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="E7" s="40" t="n">
+      <c r="C7" s="43"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="44" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>2370</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="H7" s="41" t="n">
+      <c r="F7" s="44"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="45" t="n">
         <f aca="false">B7-E7</f>
         <v>600</v>
       </c>
-      <c r="I7" s="41"/>
-      <c r="K7" s="42" t="n">
+      <c r="I7" s="45"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="46" t="n">
         <f aca="false">COUNTIFS('Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>3</v>
       </c>
-      <c r="L7" s="42"/>
-    </row>
-    <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="E9" s="38" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="F9" s="42"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="38"/>
-      <c r="K9" s="38" t="s">
+      <c r="I9" s="42"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="L9" s="38"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="43" t="n">
+      <c r="A10" s="2"/>
+      <c r="B10" s="47" t="n">
         <f aca="false">IFERROR(ROUND(SUMPRODUCT(('Income Log'!$G$6:$G$105-'Income Log'!$A$6:$A$105)*('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4))/SUMPRODUCT(('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4)*1),1),"—")</f>
         <v>10</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="E10" s="44" t="n">
+      <c r="C10" s="47"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="48" t="n">
         <f aca="false">IF(B7=0,"",E7/B7)</f>
         <v>0.797979797979798</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="H10" s="45" t="n">
+      <c r="F10" s="48"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="49" t="n">
         <f aca="false">IF(K7=0,"",B7/K7)</f>
         <v>990</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="K10" s="41" t="n">
+      <c r="I10" s="49"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="45" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Overdue",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>0</v>
       </c>
-      <c r="L10" s="41"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="L10" s="45"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="n">
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A15,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
         <v>1520</v>
       </c>
-      <c r="H15" s="47" t="str">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="51" t="str">
         <f aca="false">IF(Settings!A18="","",Settings!A18)</f>
         <v>Acme Studios</v>
       </c>
-      <c r="I15" s="48" t="n">
+      <c r="I15" s="52" t="n">
         <f aca="false">IF($H15="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H15,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>2120</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="n">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="48" t="n">
+      <c r="C16" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A16,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
         <v>850</v>
       </c>
-      <c r="H16" s="47" t="str">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="51" t="str">
         <f aca="false">IF(Settings!A19="","",Settings!A19)</f>
         <v>Beacon Coffee Co.</v>
       </c>
-      <c r="I16" s="48" t="n">
+      <c r="I16" s="52" t="n">
         <f aca="false">IF($H16="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H16,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>850</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="46" t="n">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="48" t="n">
+      <c r="C17" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A17,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
         <v>600</v>
       </c>
-      <c r="H17" s="47" t="str">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="51" t="str">
         <f aca="false">IF(Settings!A20="","",Settings!A20)</f>
         <v/>
       </c>
-      <c r="I17" s="48" t="str">
+      <c r="I17" s="52" t="str">
         <f aca="false">IF($H17="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H17,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="n">
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="48" t="n">
+      <c r="C18" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A18,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="47" t="str">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="51" t="str">
         <f aca="false">IF(Settings!A21="","",Settings!A21)</f>
         <v/>
       </c>
-      <c r="I18" s="48" t="str">
+      <c r="I18" s="52" t="str">
         <f aca="false">IF($H18="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H18,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="n">
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="48" t="n">
+      <c r="C19" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A19,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="47" t="str">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="51" t="str">
         <f aca="false">IF(Settings!A22="","",Settings!A22)</f>
         <v/>
       </c>
-      <c r="I19" s="48" t="str">
+      <c r="I19" s="52" t="str">
         <f aca="false">IF($H19="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H19,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="n">
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="48" t="n">
+      <c r="C20" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A20,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="47" t="str">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="51" t="str">
         <f aca="false">IF(Settings!A23="","",Settings!A23)</f>
         <v/>
       </c>
-      <c r="I20" s="48" t="str">
+      <c r="I20" s="52" t="str">
         <f aca="false">IF($H20="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H20,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="46" t="n">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="48" t="n">
+      <c r="C21" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A21,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="47" t="str">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="51" t="str">
         <f aca="false">IF(Settings!A24="","",Settings!A24)</f>
         <v/>
       </c>
-      <c r="I21" s="48" t="str">
+      <c r="I21" s="52" t="str">
         <f aca="false">IF($H21="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H21,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="n">
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="48" t="n">
+      <c r="C22" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A22,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="47" t="str">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="51" t="str">
         <f aca="false">IF(Settings!A25="","",Settings!A25)</f>
         <v/>
       </c>
-      <c r="I22" s="48" t="str">
+      <c r="I22" s="52" t="str">
         <f aca="false">IF($H22="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H22,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="n">
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="48" t="n">
+      <c r="C23" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A23,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="47" t="str">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="51" t="str">
         <f aca="false">IF(Settings!A26="","",Settings!A26)</f>
         <v/>
       </c>
-      <c r="I23" s="48" t="str">
+      <c r="I23" s="52" t="str">
         <f aca="false">IF($H23="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H23,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46" t="n">
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A24,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A24+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="47" t="str">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="51" t="str">
         <f aca="false">IF(Settings!A27="","",Settings!A27)</f>
         <v/>
       </c>
-      <c r="I24" s="48" t="str">
+      <c r="I24" s="52" t="str">
         <f aca="false">IF($H24="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H24,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="n">
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="48" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A25,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A25+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="49" t="str">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="53" t="str">
         <f aca="false">IF(Settings!A28="","",Settings!A28)</f>
         <v/>
       </c>
-      <c r="I25" s="50" t="str">
+      <c r="I25" s="54" t="str">
         <f aca="false">IF($H25="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H25,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46" t="n">
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="48" t="n">
+      <c r="C26" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A26,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A26+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="49" t="str">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="53" t="str">
         <f aca="false">IF(Settings!A29="","",Settings!A29)</f>
         <v/>
       </c>
-      <c r="I26" s="50" t="str">
+      <c r="I26" s="54" t="str">
         <f aca="false">IF($H26="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H26,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="49" t="str">
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="53" t="str">
         <f aca="false">IF(Settings!A30="","",Settings!A30)</f>
         <v/>
       </c>
-      <c r="I27" s="50" t="str">
+      <c r="I27" s="54" t="str">
         <f aca="false">IF($H27="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H27,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="49" t="str">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="53" t="str">
         <f aca="false">IF(Settings!A31="","",Settings!A31)</f>
         <v/>
       </c>
-      <c r="I28" s="50" t="str">
+      <c r="I28" s="54" t="str">
         <f aca="false">IF($H28="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H28,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H29" s="49" t="str">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="53" t="str">
         <f aca="false">IF(Settings!A32="","",Settings!A32)</f>
         <v/>
       </c>
-      <c r="I29" s="50" t="str">
+      <c r="I29" s="54" t="str">
         <f aca="false">IF($H29="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H29,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="46" t="n">
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="48" t="n">
+      <c r="C30" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
         <v>2970</v>
       </c>
-      <c r="D30" s="48" t="n">
+      <c r="D30" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
         <v>2370</v>
       </c>
-      <c r="H30" s="49" t="str">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="53" t="str">
         <f aca="false">IF(Settings!A33="","",Settings!A33)</f>
         <v/>
       </c>
-      <c r="I30" s="50" t="str">
+      <c r="I30" s="54" t="str">
         <f aca="false">IF($H30="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H30,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="46" t="n">
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="48" t="n">
+      <c r="C31" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="48" t="n">
+      <c r="D31" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="49" t="str">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="53" t="str">
         <f aca="false">IF(Settings!A34="","",Settings!A34)</f>
         <v/>
       </c>
-      <c r="I31" s="50" t="str">
+      <c r="I31" s="54" t="str">
         <f aca="false">IF($H31="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H31,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="46" t="n">
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="48" t="n">
+      <c r="C32" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="48" t="n">
+      <c r="D32" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H32" s="49" t="str">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="53" t="str">
         <f aca="false">IF(Settings!A35="","",Settings!A35)</f>
         <v/>
       </c>
-      <c r="I32" s="50" t="str">
+      <c r="I32" s="54" t="str">
         <f aca="false">IF($H32="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H32,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="46" t="n">
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="48" t="n">
+      <c r="C33" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="48" t="n">
+      <c r="D33" s="52" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
         <v>0</v>
       </c>
-      <c r="H33" s="49" t="str">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="53" t="str">
         <f aca="false">IF(Settings!A36="","",Settings!A36)</f>
         <v/>
       </c>
-      <c r="I33" s="50" t="str">
+      <c r="I33" s="54" t="str">
         <f aca="false">IF($H33="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H33,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H34" s="49" t="str">
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="53" t="str">
         <f aca="false">IF(Settings!A37="","",Settings!A37)</f>
         <v/>
       </c>
-      <c r="I34" s="50" t="str">
+      <c r="I34" s="54" t="str">
         <f aca="false">IF($H34="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H34,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>

--- a/products/freelance-invoice-income-tracker.xlsx
+++ b/products/freelance-invoice-income-tracker.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$M$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$M$58</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Income Log'!$A$1:$G$40</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Invoice!$A$1:$D$35</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Settings!$A$1:$D$38</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t xml:space="preserve">Freelance Invoice + Income Tracker</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIGHTS — written automatically from your numbers</t>
   </si>
 </sst>
 </file>
@@ -381,7 +384,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,6 +572,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -707,7 +718,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -926,6 +937,18 @@
     </xf>
     <xf numFmtId="171" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -937,7 +960,71 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F3A5F"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9FAFC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F2937"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCF3E4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF1D6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B7A46"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92600A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1232,11 +1319,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="46652681"/>
-        <c:axId val="12331454"/>
+        <c:axId val="81909475"/>
+        <c:axId val="19077728"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46652681"/>
+        <c:axId val="81909475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1268,7 +1355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12331454"/>
+        <c:crossAx val="19077728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1276,7 +1363,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12331454"/>
+        <c:axId val="19077728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1318,7 +1405,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46652681"/>
+        <c:crossAx val="81909475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1349,14 +1436,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>747720</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>17640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1364,7 +1451,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="281880" y="7648560"/>
+        <a:off x="281880" y="9277200"/>
         <a:ext cx="5399640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1376,6 +1463,21 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="IncomeLog" displayName="IncomeLog" ref="A5:G105" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:G105"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Client"/>
+    <tableColumn id="3" name="Invoice #"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Amount"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Date paid"/>
+  </tableColumns>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3931,19 +4033,19 @@
       <c r="G105" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F105">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Paid"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"Sent"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"Overdue"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3964,6 +4066,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3972,7 +4077,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -4812,75 +4917,89 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
+      <c r="B35" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="B36" s="57" t="str">
+        <f aca="false">IFERROR(IF($H$7=0,"Everything invoiced this year has been collected.",TEXT(COUNTIFS('Income Log'!$F$6:$F$105,"&lt;&gt;Paid",'Income Log'!$E$6:$E$105,"&gt;0",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)),"0")&amp;" invoice(s) worth "&amp;TEXT($H$7,"$#,##0")&amp;" are still unpaid."),"")</f>
+        <v>1 invoice(s) worth $600 are still unpaid.</v>
+      </c>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="B37" s="57" t="str">
+        <f aca="false">IFERROR(IF(MAX($C$15:$C$26)=0,"","Busiest month: "&amp;INDEX($B$15:$B$26,MATCH(MAX($C$15:$C$26),$C$15:$C$26,0))&amp;" ("&amp;TEXT(MAX($C$15:$C$26),"$#,##0")&amp;" invoiced)."),"")</f>
+        <v>Busiest month: January ($1,520 invoiced).</v>
+      </c>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
+      <c r="B38" s="57" t="str">
+        <f aca="true">IFERROR(IF($H$7=0,"","Oldest unpaid invoice is "&amp;TEXT(TODAY()-_xlfn.MINIFS('Income Log'!$A$6:$A$105,'Income Log'!$F$6:$F$105,"&lt;&gt;Paid",'Income Log'!$E$6:$E$105,"&gt;0"),"0")&amp;" days old — worth a nudge."),"")</f>
+        <v>Oldest unpaid invoice is 163 days old — worth a nudge.</v>
+      </c>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="B39" s="57" t="str">
+        <f aca="false">IFERROR(IF($B$7=0,"","Top client: "&amp;INDEX($H$15:$H$34,MATCH(MAX($I$15:$I$34),$I$15:$I$34,0))&amp;" — "&amp;TEXT(MAX($I$15:$I$34)/$B$7,"0%")&amp;" of the year."),"")</f>
+        <v>Top client: Acme Studios — 71% of the year.</v>
+      </c>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -5127,9 +5246,84 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
+    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
-  <mergeCells count="18">
+  <mergeCells count="22">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B6:C6"/>
@@ -5148,6 +5342,10 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>

--- a/products/freelance-invoice-income-tracker.xlsx
+++ b/products/freelance-invoice-income-tracker.xlsx
@@ -384,7 +384,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,8 +478,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF1F3A5F"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -533,15 +533,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF1F3A5F"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FF2E9E8F"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -549,7 +541,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FFB3352C"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -557,7 +549,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -625,18 +617,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF9FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF9FAFC"/>
         <bgColor rgb="FFF4F7FA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF9FAFC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -645,17 +637,20 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD8DEE9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD8DEE9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD8DEE9"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFD8DEE9"/>
+        <color rgb="FFE7EBEE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3A5F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -678,15 +673,9 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFE3E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE3E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE3E8F0"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFE3E8F0"/>
       </bottom>
@@ -718,7 +707,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -783,7 +772,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -819,6 +808,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -827,11 +820,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -843,11 +836,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -863,6 +856,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -875,59 +880,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -939,7 +932,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -947,7 +940,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -960,15 +953,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3A5F"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -988,7 +973,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF1F2937"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F3A5F"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1078,7 +1078,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFF9FAFC"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -1092,7 +1092,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF6DE"/>
-      <rgbColor rgb="FFE3E8F0"/>
+      <rgbColor rgb="FFE7EBEE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1106,12 +1106,12 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF4F7FA"/>
+      <rgbColor rgb="FFE3E8F0"/>
       <rgbColor rgb="FFDCF3E4"/>
       <rgbColor rgb="FFFFF1D6"/>
       <rgbColor rgb="FFE4E9E6"/>
       <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFF9FAFC"/>
+      <rgbColor rgb="FFF4F7FA"/>
       <rgbColor rgb="FFFBE3E1"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1319,11 +1319,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81909475"/>
-        <c:axId val="19077728"/>
+        <c:axId val="11401090"/>
+        <c:axId val="11740362"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81909475"/>
+        <c:axId val="11401090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1355,7 +1355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19077728"/>
+        <c:crossAx val="11740362"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1363,7 +1363,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19077728"/>
+        <c:axId val="11740362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1405,7 +1405,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81909475"/>
+        <c:crossAx val="11401090"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1443,7 +1443,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>747720</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1451,7 +1451,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="281880" y="9277200"/>
+        <a:off x="281880" y="9487080"/>
         <a:ext cx="5399640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2429,7 +2429,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
         <v>40</v>
       </c>
@@ -2812,17 +2812,17 @@
         <v>Acme Studios LLC</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="25" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2833,10 +2833,10 @@
       <c r="B13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="27" t="n">
         <f aca="false">IF(OR($B13="",$C13=""),"",ROUND($B13*$C13,2))</f>
         <v>600</v>
       </c>
@@ -2848,10 +2848,10 @@
       <c r="B14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <f aca="false">IF(OR($B14="",$C14=""),"",ROUND($B14*$C14,2))</f>
         <v>160</v>
       </c>
@@ -2859,8 +2859,8 @@
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26" t="str">
+      <c r="C15" s="26"/>
+      <c r="D15" s="27" t="str">
         <f aca="false">IF(OR($B15="",$C15=""),"",ROUND($B15*$C15,2))</f>
         <v/>
       </c>
@@ -2868,8 +2868,8 @@
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26" t="str">
+      <c r="C16" s="26"/>
+      <c r="D16" s="27" t="str">
         <f aca="false">IF(OR($B16="",$C16=""),"",ROUND($B16*$C16,2))</f>
         <v/>
       </c>
@@ -2877,8 +2877,8 @@
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26" t="str">
+      <c r="C17" s="26"/>
+      <c r="D17" s="27" t="str">
         <f aca="false">IF(OR($B17="",$C17=""),"",ROUND($B17*$C17,2))</f>
         <v/>
       </c>
@@ -2886,8 +2886,8 @@
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26" t="str">
+      <c r="C18" s="26"/>
+      <c r="D18" s="27" t="str">
         <f aca="false">IF(OR($B18="",$C18=""),"",ROUND($B18*$C18,2))</f>
         <v/>
       </c>
@@ -2895,8 +2895,8 @@
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26" t="str">
+      <c r="C19" s="26"/>
+      <c r="D19" s="27" t="str">
         <f aca="false">IF(OR($B19="",$C19=""),"",ROUND($B19*$C19,2))</f>
         <v/>
       </c>
@@ -2904,8 +2904,8 @@
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26" t="str">
+      <c r="C20" s="26"/>
+      <c r="D20" s="27" t="str">
         <f aca="false">IF(OR($B20="",$C20=""),"",ROUND($B20*$C20,2))</f>
         <v/>
       </c>
@@ -2913,8 +2913,8 @@
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="26" t="str">
+      <c r="C21" s="26"/>
+      <c r="D21" s="27" t="str">
         <f aca="false">IF(OR($B21="",$C21=""),"",ROUND($B21*$C21,2))</f>
         <v/>
       </c>
@@ -2922,8 +2922,8 @@
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26" t="str">
+      <c r="C22" s="26"/>
+      <c r="D22" s="27" t="str">
         <f aca="false">IF(OR($B22="",$C22=""),"",ROUND($B22*$C22,2))</f>
         <v/>
       </c>
@@ -2931,8 +2931,8 @@
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26" t="str">
+      <c r="C23" s="26"/>
+      <c r="D23" s="27" t="str">
         <f aca="false">IF(OR($B23="",$C23=""),"",ROUND($B23*$C23,2))</f>
         <v/>
       </c>
@@ -2940,36 +2940,36 @@
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26" t="str">
+      <c r="C24" s="26"/>
+      <c r="D24" s="27" t="str">
         <f aca="false">IF(OR($B24="",$C24=""),"",ROUND($B24*$C24,2))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="29" t="n">
         <f aca="false">SUM(D13:D24)</f>
         <v>760</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="29" t="str">
+      <c r="C27" s="30" t="str">
         <f aca="false">"Tax ("&amp;TEXT(Settings!$B$12,"0.0%")&amp;")"</f>
         <v>Tax (8.5%)</v>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="D27" s="31" t="n">
         <f aca="false">ROUND(D26*Settings!$B$12,2)</f>
         <v>64.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="32" t="n">
+      <c r="D28" s="33" t="n">
         <f aca="false">D26+D27</f>
         <v>824.6</v>
       </c>
@@ -2980,21 +2980,21 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="str">
+      <c r="A32" s="34" t="str">
         <f aca="false">IF(Settings!B9="","",Settings!B9)</f>
         <v>Pay by bank transfer to a/c 0000-1111 or PayPal alex@riveradesign.com</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -3065,972 +3065,972 @@
       <c r="H2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="37" t="n">
         <v>46034</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="39" t="n">
         <v>1520</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="36" t="n">
+      <c r="G6" s="37" t="n">
         <v>46042</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="40" t="n">
         <v>46056</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="41" t="n">
+      <c r="E7" s="42" t="n">
         <v>850</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="40" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="37" t="n">
         <v>46083</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="36"/>
+      <c r="G8" s="37"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="39"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="36"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="39"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="36"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="39"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="36"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="39"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="37"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="39"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="36"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="37"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="39"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="36"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="37"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="39"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="36"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="37"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="39"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="39"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="37"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="39"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="36"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="36"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="37"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="39"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="40"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="37"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="39"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="36"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="36"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="37"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="39"/>
+      <c r="A33" s="40"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="36"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="36"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="37"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="39"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="40"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="36"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="37"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="39"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="39"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="36"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="36"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="37"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="39"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="39"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="36"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="37"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="39"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="39"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="40"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="36"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="37"/>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="39"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="40"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="36"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="37"/>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="39"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="39"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="40"/>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="36"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="36"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="37"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="39"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="40"/>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="36"/>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="36"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="37"/>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="39"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="39"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="40"/>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="36"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="36"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="37"/>
     </row>
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="39"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="39"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="36"/>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="36"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="37"/>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="39"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="39"/>
+      <c r="A53" s="40"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="40"/>
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="36"/>
-      <c r="B54" s="37"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="36"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="37"/>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="39"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="39"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="40"/>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="36"/>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="36"/>
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="37"/>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="39"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="39"/>
+      <c r="A57" s="40"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="40"/>
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="36"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="36"/>
+      <c r="A58" s="37"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="37"/>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="39"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="39"/>
+      <c r="A59" s="40"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="40"/>
     </row>
     <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="36"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="36"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="37"/>
     </row>
     <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="39"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="39"/>
+      <c r="A61" s="40"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="40"/>
     </row>
     <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="36"/>
-      <c r="B62" s="37"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="36"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="37"/>
     </row>
     <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="39"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="39"/>
+      <c r="A63" s="40"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="40"/>
     </row>
     <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="36"/>
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="36"/>
+      <c r="A64" s="37"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="37"/>
     </row>
     <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="39"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="39"/>
+      <c r="A65" s="40"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="40"/>
     </row>
     <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="36"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="36"/>
+      <c r="A66" s="37"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="37"/>
     </row>
     <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="39"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="39"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="40"/>
     </row>
     <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="36"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="36"/>
+      <c r="A68" s="37"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="37"/>
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="39"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="39"/>
+      <c r="A69" s="40"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="40"/>
     </row>
     <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="36"/>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="36"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="37"/>
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="39"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="39"/>
+      <c r="A71" s="40"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="40"/>
     </row>
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="36"/>
-      <c r="B72" s="37"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="36"/>
+      <c r="A72" s="37"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="37"/>
     </row>
     <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="39"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="39"/>
+      <c r="A73" s="40"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="40"/>
     </row>
     <row r="74" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="36"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="36"/>
+      <c r="A74" s="37"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="37"/>
     </row>
     <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="39"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="39"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="40"/>
     </row>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="36"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="36"/>
+      <c r="A76" s="37"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="37"/>
     </row>
     <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="39"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="41"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="39"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="40"/>
     </row>
     <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="36"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="36"/>
+      <c r="A78" s="37"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="37"/>
     </row>
     <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="39"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="39"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="40"/>
     </row>
     <row r="80" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="36"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="36"/>
+      <c r="A80" s="37"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="39"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="39"/>
+      <c r="A81" s="40"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="40"/>
     </row>
     <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="36"/>
-      <c r="B82" s="37"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="36"/>
+      <c r="A82" s="37"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="37"/>
     </row>
     <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="39"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="41"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="39"/>
+      <c r="A83" s="40"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="40"/>
     </row>
     <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="36"/>
-      <c r="B84" s="37"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="38"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="36"/>
+      <c r="A84" s="37"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="37"/>
     </row>
     <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="39"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="39"/>
+      <c r="A85" s="40"/>
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="40"/>
     </row>
     <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="36"/>
-      <c r="B86" s="37"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="36"/>
+      <c r="A86" s="37"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="37"/>
     </row>
     <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="39"/>
-      <c r="B87" s="40"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="39"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="40"/>
     </row>
     <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="36"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="36"/>
+      <c r="A88" s="37"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="37"/>
     </row>
     <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="39"/>
-      <c r="B89" s="40"/>
-      <c r="C89" s="40"/>
-      <c r="D89" s="40"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="40"/>
-      <c r="G89" s="39"/>
+      <c r="A89" s="40"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="40"/>
     </row>
     <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="36"/>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="36"/>
+      <c r="A90" s="37"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="38"/>
+      <c r="G90" s="37"/>
     </row>
     <row r="91" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="39"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="40"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="40"/>
-      <c r="G91" s="39"/>
+      <c r="A91" s="40"/>
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="40"/>
     </row>
     <row r="92" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="36"/>
-      <c r="B92" s="37"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="36"/>
+      <c r="A92" s="37"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="37"/>
     </row>
     <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="39"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="40"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="40"/>
-      <c r="G93" s="39"/>
+      <c r="A93" s="40"/>
+      <c r="B93" s="41"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="41"/>
+      <c r="G93" s="40"/>
     </row>
     <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="36"/>
-      <c r="B94" s="37"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="37"/>
-      <c r="G94" s="36"/>
+      <c r="A94" s="37"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="39"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="37"/>
     </row>
     <row r="95" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="39"/>
-      <c r="B95" s="40"/>
-      <c r="C95" s="40"/>
-      <c r="D95" s="40"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="40"/>
-      <c r="G95" s="39"/>
+      <c r="A95" s="40"/>
+      <c r="B95" s="41"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="41"/>
+      <c r="G95" s="40"/>
     </row>
     <row r="96" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="36"/>
-      <c r="B96" s="37"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="37"/>
-      <c r="G96" s="36"/>
+      <c r="A96" s="37"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="39"/>
+      <c r="F96" s="38"/>
+      <c r="G96" s="37"/>
     </row>
     <row r="97" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="39"/>
-      <c r="B97" s="40"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="40"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="40"/>
-      <c r="G97" s="39"/>
+      <c r="A97" s="40"/>
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="40"/>
     </row>
     <row r="98" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="36"/>
-      <c r="B98" s="37"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="36"/>
+      <c r="A98" s="37"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="37"/>
     </row>
     <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="39"/>
-      <c r="B99" s="40"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="40"/>
-      <c r="E99" s="41"/>
-      <c r="F99" s="40"/>
-      <c r="G99" s="39"/>
+      <c r="A99" s="40"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="40"/>
     </row>
     <row r="100" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="36"/>
-      <c r="B100" s="37"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="38"/>
-      <c r="F100" s="37"/>
-      <c r="G100" s="36"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="37"/>
     </row>
     <row r="101" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="39"/>
-      <c r="B101" s="40"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="40"/>
-      <c r="E101" s="41"/>
-      <c r="F101" s="40"/>
-      <c r="G101" s="39"/>
+      <c r="A101" s="40"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="42"/>
+      <c r="F101" s="41"/>
+      <c r="G101" s="40"/>
     </row>
     <row r="102" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="36"/>
-      <c r="B102" s="37"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="37"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="37"/>
-      <c r="G102" s="36"/>
+      <c r="A102" s="37"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="38"/>
+      <c r="G102" s="37"/>
     </row>
     <row r="103" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="39"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="40"/>
-      <c r="E103" s="41"/>
-      <c r="F103" s="40"/>
-      <c r="G103" s="39"/>
+      <c r="A103" s="40"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="41"/>
+      <c r="D103" s="41"/>
+      <c r="E103" s="42"/>
+      <c r="F103" s="41"/>
+      <c r="G103" s="40"/>
     </row>
     <row r="104" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="36"/>
-      <c r="B104" s="37"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="37"/>
-      <c r="E104" s="38"/>
-      <c r="F104" s="37"/>
-      <c r="G104" s="36"/>
+      <c r="A104" s="37"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="38"/>
+      <c r="G104" s="37"/>
     </row>
     <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="39"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="40"/>
-      <c r="E105" s="41"/>
-      <c r="F105" s="40"/>
-      <c r="G105" s="39"/>
+      <c r="A105" s="40"/>
+      <c r="B105" s="41"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="41"/>
+      <c r="E105" s="42"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="40"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
@@ -4039,13 +4039,13 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F105">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"Paid"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"Sent"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Overdue"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4174,54 +4174,54 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="43"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="42"/>
+      <c r="F6" s="43"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="42"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="42"/>
+      <c r="L6" s="43"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="44" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>2970</v>
       </c>
-      <c r="C7" s="43"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="45" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>2370</v>
       </c>
-      <c r="F7" s="44"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">B7-E7</f>
         <v>600</v>
       </c>
-      <c r="I7" s="45"/>
+      <c r="I7" s="46"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="47" t="n">
         <f aca="false">COUNTIFS('Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>3</v>
       </c>
-      <c r="L7" s="46"/>
+      <c r="L7" s="47"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4239,54 +4239,54 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="42"/>
+      <c r="F9" s="43"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="42"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="42" t="s">
+      <c r="K9" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="L9" s="42"/>
+      <c r="L9" s="43"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="48" t="n">
         <f aca="false">IFERROR(ROUND(SUMPRODUCT(('Income Log'!$G$6:$G$105-'Income Log'!$A$6:$A$105)*('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4))/SUMPRODUCT(('Income Log'!$G$6:$G$105&lt;&gt;"")*(YEAR('Income Log'!$A$6:$A$105)=$C$4)*1),1),"—")</f>
         <v>10</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="49" t="n">
         <f aca="false">IF(B7=0,"",E7/B7)</f>
         <v>0.797979797979798</v>
       </c>
-      <c r="F10" s="48"/>
+      <c r="F10" s="49"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="49" t="n">
+      <c r="H10" s="50" t="n">
         <f aca="false">IF(K7=0,"",B7/K7)</f>
         <v>990</v>
       </c>
-      <c r="I10" s="49"/>
+      <c r="I10" s="50"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="45" t="n">
+      <c r="K10" s="46" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Overdue",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>0</v>
       </c>
-      <c r="L10" s="45"/>
+      <c r="L10" s="46"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4338,7 +4338,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
         <v>89</v>
       </c>
@@ -4364,13 +4364,13 @@
       <c r="M14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="52" t="n">
+      <c r="C15" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A15,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
         <v>1520</v>
       </c>
@@ -4378,11 +4378,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="51" t="str">
+      <c r="H15" s="52" t="str">
         <f aca="false">IF(Settings!A18="","",Settings!A18)</f>
         <v>Acme Studios</v>
       </c>
-      <c r="I15" s="52" t="n">
+      <c r="I15" s="53" t="n">
         <f aca="false">IF($H15="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H15,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>2120</v>
       </c>
@@ -4392,13 +4392,13 @@
       <c r="M15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="52" t="n">
+      <c r="C16" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A16,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
         <v>850</v>
       </c>
@@ -4406,11 +4406,11 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="51" t="str">
+      <c r="H16" s="52" t="str">
         <f aca="false">IF(Settings!A19="","",Settings!A19)</f>
         <v>Beacon Coffee Co.</v>
       </c>
-      <c r="I16" s="52" t="n">
+      <c r="I16" s="53" t="n">
         <f aca="false">IF($H16="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H16,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>850</v>
       </c>
@@ -4420,13 +4420,13 @@
       <c r="M16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="n">
+      <c r="A17" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="52" t="n">
+      <c r="C17" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A17,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
         <v>600</v>
       </c>
@@ -4434,11 +4434,11 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="51" t="str">
+      <c r="H17" s="52" t="str">
         <f aca="false">IF(Settings!A20="","",Settings!A20)</f>
         <v/>
       </c>
-      <c r="I17" s="52" t="str">
+      <c r="I17" s="53" t="str">
         <f aca="false">IF($H17="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H17,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4448,13 +4448,13 @@
       <c r="M17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="52" t="n">
+      <c r="C18" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A18,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
         <v>0</v>
       </c>
@@ -4462,11 +4462,11 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="51" t="str">
+      <c r="H18" s="52" t="str">
         <f aca="false">IF(Settings!A21="","",Settings!A21)</f>
         <v/>
       </c>
-      <c r="I18" s="52" t="str">
+      <c r="I18" s="53" t="str">
         <f aca="false">IF($H18="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H18,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4476,13 +4476,13 @@
       <c r="M18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A19,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
         <v>0</v>
       </c>
@@ -4490,11 +4490,11 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="51" t="str">
+      <c r="H19" s="52" t="str">
         <f aca="false">IF(Settings!A22="","",Settings!A22)</f>
         <v/>
       </c>
-      <c r="I19" s="52" t="str">
+      <c r="I19" s="53" t="str">
         <f aca="false">IF($H19="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H19,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4504,13 +4504,13 @@
       <c r="M19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="52" t="n">
+      <c r="C20" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A20,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
         <v>0</v>
       </c>
@@ -4518,11 +4518,11 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="51" t="str">
+      <c r="H20" s="52" t="str">
         <f aca="false">IF(Settings!A23="","",Settings!A23)</f>
         <v/>
       </c>
-      <c r="I20" s="52" t="str">
+      <c r="I20" s="53" t="str">
         <f aca="false">IF($H20="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H20,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4532,13 +4532,13 @@
       <c r="M20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A21,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
         <v>0</v>
       </c>
@@ -4546,11 +4546,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="51" t="str">
+      <c r="H21" s="52" t="str">
         <f aca="false">IF(Settings!A24="","",Settings!A24)</f>
         <v/>
       </c>
-      <c r="I21" s="52" t="str">
+      <c r="I21" s="53" t="str">
         <f aca="false">IF($H21="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H21,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4560,13 +4560,13 @@
       <c r="M21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A22,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
         <v>0</v>
       </c>
@@ -4574,11 +4574,11 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="51" t="str">
+      <c r="H22" s="52" t="str">
         <f aca="false">IF(Settings!A25="","",Settings!A25)</f>
         <v/>
       </c>
-      <c r="I22" s="52" t="str">
+      <c r="I22" s="53" t="str">
         <f aca="false">IF($H22="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H22,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4588,13 +4588,13 @@
       <c r="M22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A23,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
         <v>0</v>
       </c>
@@ -4602,11 +4602,11 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="51" t="str">
+      <c r="H23" s="52" t="str">
         <f aca="false">IF(Settings!A26="","",Settings!A26)</f>
         <v/>
       </c>
-      <c r="I23" s="52" t="str">
+      <c r="I23" s="53" t="str">
         <f aca="false">IF($H23="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H23,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4616,13 +4616,13 @@
       <c r="M23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="52" t="n">
+      <c r="C24" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A24,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A24+1,1))</f>
         <v>0</v>
       </c>
@@ -4630,11 +4630,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="51" t="str">
+      <c r="H24" s="52" t="str">
         <f aca="false">IF(Settings!A27="","",Settings!A27)</f>
         <v/>
       </c>
-      <c r="I24" s="52" t="str">
+      <c r="I24" s="53" t="str">
         <f aca="false">IF($H24="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H24,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4644,13 +4644,13 @@
       <c r="M24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A25,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A25+1,1))</f>
         <v>0</v>
       </c>
@@ -4658,11 +4658,11 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="53" t="str">
+      <c r="H25" s="54" t="str">
         <f aca="false">IF(Settings!A28="","",Settings!A28)</f>
         <v/>
       </c>
-      <c r="I25" s="54" t="str">
+      <c r="I25" s="55" t="str">
         <f aca="false">IF($H25="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H25,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4672,13 +4672,13 @@
       <c r="M25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="52" t="n">
+      <c r="C26" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,$A26,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,$A26+1,1))</f>
         <v>0</v>
       </c>
@@ -4686,11 +4686,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="53" t="str">
+      <c r="H26" s="54" t="str">
         <f aca="false">IF(Settings!A29="","",Settings!A29)</f>
         <v/>
       </c>
-      <c r="I26" s="54" t="str">
+      <c r="I26" s="55" t="str">
         <f aca="false">IF($H26="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H26,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4707,11 +4707,11 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="53" t="str">
+      <c r="H27" s="54" t="str">
         <f aca="false">IF(Settings!A30="","",Settings!A30)</f>
         <v/>
       </c>
-      <c r="I27" s="54" t="str">
+      <c r="I27" s="55" t="str">
         <f aca="false">IF($H27="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H27,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4730,11 +4730,11 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="53" t="str">
+      <c r="H28" s="54" t="str">
         <f aca="false">IF(Settings!A31="","",Settings!A31)</f>
         <v/>
       </c>
-      <c r="I28" s="54" t="str">
+      <c r="I28" s="55" t="str">
         <f aca="false">IF($H28="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H28,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4743,7 +4743,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
         <v>89</v>
       </c>
@@ -4759,11 +4759,11 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="53" t="str">
+      <c r="H29" s="54" t="str">
         <f aca="false">IF(Settings!A32="","",Settings!A32)</f>
         <v/>
       </c>
-      <c r="I29" s="54" t="str">
+      <c r="I29" s="55" t="str">
         <f aca="false">IF($H29="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H29,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4773,28 +4773,28 @@
       <c r="M29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="50" t="n">
+      <c r="A30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="52" t="n">
+      <c r="C30" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
         <v>2970</v>
       </c>
-      <c r="D30" s="52" t="n">
+      <c r="D30" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A30-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
         <v>2370</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="53" t="str">
+      <c r="H30" s="54" t="str">
         <f aca="false">IF(Settings!A33="","",Settings!A33)</f>
         <v/>
       </c>
-      <c r="I30" s="54" t="str">
+      <c r="I30" s="55" t="str">
         <f aca="false">IF($H30="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H30,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4804,28 +4804,28 @@
       <c r="M30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="n">
+      <c r="A31" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="52" t="n">
+      <c r="C31" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="52" t="n">
+      <c r="D31" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A31-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A31+1,1))</f>
         <v>0</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="53" t="str">
+      <c r="H31" s="54" t="str">
         <f aca="false">IF(Settings!A34="","",Settings!A34)</f>
         <v/>
       </c>
-      <c r="I31" s="54" t="str">
+      <c r="I31" s="55" t="str">
         <f aca="false">IF($H31="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H31,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4835,28 +4835,28 @@
       <c r="M31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="50" t="n">
+      <c r="A32" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="52" t="n">
+      <c r="C32" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="52" t="n">
+      <c r="D32" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A32-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A32+1,1))</f>
         <v>0</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="53" t="str">
+      <c r="H32" s="54" t="str">
         <f aca="false">IF(Settings!A35="","",Settings!A35)</f>
         <v/>
       </c>
-      <c r="I32" s="54" t="str">
+      <c r="I32" s="55" t="str">
         <f aca="false">IF($H32="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H32,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4866,28 +4866,28 @@
       <c r="M32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="52" t="n">
+      <c r="C33" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="52" t="n">
+      <c r="D33" s="53" t="n">
         <f aca="false">SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$F$6:$F$105,"Paid",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,3*$A33-2,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4,3*$A33+1,1))</f>
         <v>0</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="53" t="str">
+      <c r="H33" s="54" t="str">
         <f aca="false">IF(Settings!A36="","",Settings!A36)</f>
         <v/>
       </c>
-      <c r="I33" s="54" t="str">
+      <c r="I33" s="55" t="str">
         <f aca="false">IF($H33="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H33,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4904,11 +4904,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="53" t="str">
+      <c r="H34" s="54" t="str">
         <f aca="false">IF(Settings!A37="","",Settings!A37)</f>
         <v/>
       </c>
-      <c r="I34" s="54" t="str">
+      <c r="I34" s="55" t="str">
         <f aca="false">IF($H34="","",SUMIFS('Income Log'!$E$6:$E$105,'Income Log'!$B$6:$B$105,$H34,'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -4919,33 +4919,33 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
       <c r="M35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
-      <c r="B36" s="57" t="str">
+      <c r="B36" s="58" t="str">
         <f aca="false">IFERROR(IF($H$7=0,"Everything invoiced this year has been collected.",TEXT(COUNTIFS('Income Log'!$F$6:$F$105,"&lt;&gt;Paid",'Income Log'!$E$6:$E$105,"&gt;0",'Income Log'!$A$6:$A$105,"&gt;="&amp;DATE($C$4,1,1),'Income Log'!$A$6:$A$105,"&lt;"&amp;DATE($C$4+1,1,1)),"0")&amp;" invoice(s) worth "&amp;TEXT($H$7,"$#,##0")&amp;" are still unpaid."),"")</f>
         <v>1 invoice(s) worth $600 are still unpaid.</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4954,16 +4954,16 @@
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
-      <c r="B37" s="57" t="str">
+      <c r="B37" s="58" t="str">
         <f aca="false">IFERROR(IF(MAX($C$15:$C$26)=0,"","Busiest month: "&amp;INDEX($B$15:$B$26,MATCH(MAX($C$15:$C$26),$C$15:$C$26,0))&amp;" ("&amp;TEXT(MAX($C$15:$C$26),"$#,##0")&amp;" invoiced)."),"")</f>
         <v>Busiest month: January ($1,520 invoiced).</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -4972,16 +4972,16 @@
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
-      <c r="B38" s="57" t="str">
+      <c r="B38" s="58" t="str">
         <f aca="true">IFERROR(IF($H$7=0,"","Oldest unpaid invoice is "&amp;TEXT(TODAY()-_xlfn.MINIFS('Income Log'!$A$6:$A$105,'Income Log'!$F$6:$F$105,"&lt;&gt;Paid",'Income Log'!$E$6:$E$105,"&gt;0"),"0")&amp;" days old — worth a nudge."),"")</f>
         <v>Oldest unpaid invoice is 163 days old — worth a nudge.</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -4990,16 +4990,16 @@
     </row>
     <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
-      <c r="B39" s="57" t="str">
+      <c r="B39" s="58" t="str">
         <f aca="false">IFERROR(IF($B$7=0,"","Top client: "&amp;INDEX($H$15:$H$34,MATCH(MAX($I$15:$I$34),$I$15:$I$34,0))&amp;" — "&amp;TEXT(MAX($I$15:$I$34)/$B$7,"0%")&amp;" of the year."),"")</f>
         <v>Top client: Acme Studios — 71% of the year.</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
